--- a/data/gravel/Mason Raw 2025.xlsx
+++ b/data/gravel/Mason Raw 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8465FFB-3947-3646-94D3-7140DC15BBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93804B38-F3DA-0648-908D-C9FBFA277AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32820" yWindow="-23320" windowWidth="26100" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t>a8:f37</t>
+  </si>
+  <si>
+    <t>https://masoncycles.cc/images/000/009/524/large/RAWudh_AO_Side_RockShox_GX_Web-InSitu.jpg?1744386682</t>
   </si>
 </sst>
 </file>
@@ -823,6 +826,11 @@
         <v>111</v>
       </c>
     </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Mason Raw 2025.xlsx
+++ b/data/gravel/Mason Raw 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93804B38-F3DA-0648-908D-C9FBFA277AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973F923C-4874-C24C-9B98-953774924178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32820" yWindow="-23320" windowWidth="26100" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -414,6 +414,12 @@
   </si>
   <si>
     <t>https://masoncycles.cc/images/000/009/524/large/RAWudh_AO_Side_RockShox_GX_Web-InSitu.jpg?1744386682</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Lancing, West Sussex, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -778,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1738,6 +1744,14 @@
         <v>110</v>
       </c>
     </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Mason Raw 2025.xlsx
+++ b/data/gravel/Mason Raw 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973F923C-4874-C24C-9B98-953774924178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF6269C-A670-6B44-A966-B85007DD612E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -420,6 +420,24 @@
   </si>
   <si>
     <t>Lancing, West Sussex, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -784,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1581,174 +1599,204 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="1">
-        <v>31.6</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" s="1">
-        <v>34</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B60" s="1">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="1">
-        <v>180</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B62" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
+      </c>
+      <c r="B64" s="1">
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B66" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B67" s="1">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
+      </c>
+      <c r="B73" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B74" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B75" s="1">
-        <v>4300</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B81" s="1">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>128</v>
       </c>
     </row>

--- a/data/gravel/Mason Raw 2025.xlsx
+++ b/data/gravel/Mason Raw 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF6269C-A670-6B44-A966-B85007DD612E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E59C79C-ED72-F642-9513-1E86ACCF13B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8880" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="137">
   <si>
     <t>brand</t>
   </si>
@@ -410,9 +410,6 @@
     <t>threaded 73</t>
   </si>
   <si>
-    <t>a8:f37</t>
-  </si>
-  <si>
     <t>https://masoncycles.cc/images/000/009/524/large/RAWudh_AO_Side_RockShox_GX_Web-InSitu.jpg?1744386682</t>
   </si>
   <si>
@@ -438,6 +435,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f39</t>
   </si>
 </sst>
 </file>
@@ -802,7 +808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -852,7 +858,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -860,7 +866,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1391,413 +1397,450 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="C33" s="5">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="D33" s="5">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="E33" s="5">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="F33" s="5">
-        <v>700</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="C34" s="5">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="D34" s="5">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="E34" s="5">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C35" s="5">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="D35" s="5">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="E35" s="5">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="F35" s="5">
-        <v>2.6</v>
+        <v>700</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C36" s="5">
-        <v>162</v>
+        <v>2.4</v>
       </c>
       <c r="D36" s="5">
-        <v>168</v>
+        <v>2.4</v>
       </c>
       <c r="E36" s="5">
-        <v>178</v>
+        <v>2.4</v>
       </c>
       <c r="F36" s="5">
-        <v>186</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C37" s="5">
-        <v>170</v>
+        <v>2.6</v>
       </c>
       <c r="D37" s="5">
-        <v>180</v>
+        <v>2.6</v>
       </c>
       <c r="E37" s="5">
-        <v>188</v>
+        <v>2.6</v>
       </c>
       <c r="F37" s="5">
-        <v>198</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="C38" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>95</v>
+      <c r="A38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="5">
+        <v>162</v>
+      </c>
+      <c r="D38" s="5">
+        <v>168</v>
+      </c>
+      <c r="E38" s="5">
+        <v>178</v>
+      </c>
+      <c r="F38" s="5">
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="C39" s="5">
+        <v>170</v>
+      </c>
+      <c r="D39" s="5">
+        <v>180</v>
+      </c>
+      <c r="E39" s="5">
+        <v>188</v>
+      </c>
+      <c r="F39" s="5">
+        <v>198</v>
+      </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>103</v>
+      <c r="C40" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>106</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="1">
-        <v>2.6</v>
+        <v>32</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B48" s="1">
-        <v>120</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B50" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="B51" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="1">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="1">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>129</v>
+        <v>40</v>
+      </c>
+      <c r="B54" s="1">
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>130</v>
+        <v>41</v>
+      </c>
+      <c r="B55" s="1">
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="1">
-        <v>31.6</v>
+        <v>42</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B64" s="1">
-        <v>34</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B66" s="1">
-        <v>180</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B67" s="1">
-        <v>180</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="B68" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>71</v>
+        <v>49</v>
+      </c>
+      <c r="B69" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B73" s="1">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B74" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B75" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="B76" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B80" s="1">
-        <v>2600</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B81" s="1">
-        <v>4300</v>
+        <v>61</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="B82" s="1">
+        <v>2600</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>110</v>
+        <v>63</v>
+      </c>
+      <c r="B83" s="1">
+        <v>4300</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Mason Raw 2025.xlsx
+++ b/data/gravel/Mason Raw 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E59C79C-ED72-F642-9513-1E86ACCF13B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DAA20E-1837-E242-BE08-D698C05FF6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8880" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10660" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="139">
   <si>
     <t>brand</t>
   </si>
@@ -356,9 +356,6 @@
     <t>flat bar</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>rear_axle_spec</t>
   </si>
   <si>
@@ -444,13 +441,22 @@
   </si>
   <si>
     <t>a8:f39</t>
+  </si>
+  <si>
+    <t>ZS44</t>
+  </si>
+  <si>
+    <t>EC44</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -483,6 +489,12 @@
       <color rgb="FF000000"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF020203"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -504,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -512,6 +524,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -829,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -853,12 +866,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -866,7 +879,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1057,7 +1070,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17" s="6">
         <v>735</v>
@@ -1114,10 +1127,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" s="1">
         <v>118.6</v>
@@ -1152,7 +1165,7 @@
         <v>530</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="21" customHeight="1">
@@ -1219,24 +1232,24 @@
         <v>75.37</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C25" s="1">
         <f>VALUE(RIGHT(G24,3))</f>
@@ -1280,7 +1293,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C27" s="5">
         <v>800</v>
@@ -1297,7 +1310,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>89</v>
@@ -1397,7 +1410,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C33" s="5">
         <v>120</v>
@@ -1414,20 +1427,12 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C34" s="5">
-        <v>0</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5">
-        <v>0</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
@@ -1561,7 +1566,7 @@
         <v>105</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1569,7 +1574,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1642,32 +1647,38 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="23">
+      <c r="A57" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="1" t="s">
-        <v>129</v>
+      <c r="B57" s="7" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1675,7 +1686,7 @@
         <v>42</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1832,15 +1843,15 @@
         <v>65</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
